--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487442_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487442_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>D. WILLIAM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6885</v>
+        <v>6.872</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4954</v>
+        <v>5.5824</v>
       </c>
       <c r="F2" t="n">
-        <v>5.1932</v>
+        <v>1.2897</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7849</v>
+        <v>2.6177</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0849</v>
+        <v>2.1327</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8698</v>
+        <v>0.485</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1849</v>
+        <v>5.7134</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6087</v>
+        <v>4.168</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5762</v>
+        <v>1.5454</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4</v>
+        <v>-3.0957</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6936</v>
+        <v>-2.0353</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2937</v>
+        <v>-1.0604</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1336</v>
+        <v>3.5253</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2365</v>
+        <v>0.3119</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4429</v>
+        <v>-0.2153</v>
       </c>
       <c r="U2" t="n">
-        <v>2.7937</v>
+        <v>0.5271</v>
       </c>
       <c r="V2" t="n">
-        <v>1.492</v>
+        <v>2.3756</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8260999999999999</v>
+        <v>2.0427</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6659</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. WILLIAM</t>
+          <t>A. CORBACHO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4894</v>
+        <v>6.7253</v>
       </c>
       <c r="E3" t="n">
-        <v>5.173</v>
+        <v>5.1415</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3164</v>
+        <v>1.5838</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6177</v>
+        <v>4.653</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1327</v>
+        <v>0.2437</v>
       </c>
       <c r="I3" t="n">
-        <v>0.485</v>
+        <v>4.4093</v>
       </c>
       <c r="J3" t="n">
-        <v>5.7134</v>
+        <v>5.6468</v>
       </c>
       <c r="K3" t="n">
-        <v>4.168</v>
+        <v>1.5311</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5454</v>
+        <v>4.1157</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.0957</v>
+        <v>-0.9938</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0353</v>
+        <v>-1.2874</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0604</v>
+        <v>0.2937</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5668</v>
+        <v>2.9377</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.5253</v>
+        <v>2.9377</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0708</v>
+        <v>-0.5326</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6246</v>
+        <v>-0.1723</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5538999999999999</v>
+        <v>-0.3602</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3756</v>
+        <v>-0.3329</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0427</v>
+        <v>-0.3329</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CORBACHO DE LA CRUZ</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9463</v>
+        <v>5.045</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6298</v>
+        <v>1.1884</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3165</v>
+        <v>3.8566</v>
       </c>
       <c r="G4" t="n">
-        <v>4.653</v>
+        <v>0.7849</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2437</v>
+        <v>-1.0849</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4093</v>
+        <v>1.8698</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6468</v>
+        <v>2.1849</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5311</v>
+        <v>0.6087</v>
       </c>
       <c r="L4" t="n">
-        <v>4.1157</v>
+        <v>1.5762</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9938</v>
+        <v>-1.4</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2874</v>
+        <v>-1.6936</v>
       </c>
       <c r="O4" t="n">
         <v>0.2937</v>
       </c>
       <c r="P4" t="n">
-        <v>2.9377</v>
+        <v>1.1751</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9377</v>
+        <v>3.1336</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3115</v>
+        <v>1.593</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.1359</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6274999999999999</v>
+        <v>1.4571</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3329</v>
+        <v>1.492</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3329</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3878</v>
+        <v>3.94</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1694</v>
+        <v>2.374</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2184</v>
+        <v>1.5659</v>
       </c>
       <c r="G5" t="n">
         <v>0.7922</v>
@@ -844,13 +844,13 @@
         <v>2.9377</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6946</v>
+        <v>-0.1425</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8028</v>
+        <v>-0.5981</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1082</v>
+        <v>0.4557</v>
       </c>
       <c r="V5" t="n">
         <v>1.3318</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5731</v>
+        <v>2.4974</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2501</v>
+        <v>4.1477</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.677</v>
+        <v>-1.6503</v>
       </c>
       <c r="G6" t="n">
         <v>1.3024</v>
@@ -922,13 +922,13 @@
         <v>0.5875</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3501</v>
+        <v>0.2745</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3852</v>
+        <v>0.2829</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0351</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0.3329</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.038</v>
+        <v>2.0877</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7332</v>
+        <v>2.2215</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6952</v>
+        <v>-0.1338</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2054</v>
@@ -1000,13 +1000,13 @@
         <v>3.3294</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0481</v>
+        <v>0.0016</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6211</v>
+        <v>0.1094</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6691</v>
+        <v>-0.1078</v>
       </c>
       <c r="V7" t="n">
         <v>0.9412</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7968</v>
+        <v>-1.1618</v>
       </c>
       <c r="E8" t="n">
-        <v>0.077</v>
+        <v>-0.1277</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8737</v>
+        <v>-1.0341</v>
       </c>
       <c r="G8" t="n">
         <v>-1.5395</v>
@@ -1078,13 +1078,13 @@
         <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5641</v>
+        <v>0.1991</v>
       </c>
       <c r="T8" t="n">
-        <v>0.207</v>
+        <v>0.0023</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3571</v>
+        <v>0.1967</v>
       </c>
       <c r="V8" t="n">
         <v>1.5495</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5947</v>
+        <v>-3.4564</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5182</v>
+        <v>-2.6206</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0765</v>
+        <v>-0.8359</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3968</v>
@@ -1156,13 +1156,13 @@
         <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3321</v>
+        <v>0.4704</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1476</v>
+        <v>0.0453</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1845</v>
+        <v>0.4251</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5507</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9337</v>
+        <v>-3.7512</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.586</v>
+        <v>-1.4837</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3477</v>
+        <v>-2.2675</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7116</v>
@@ -1234,13 +1234,13 @@
         <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5758</v>
+        <v>-0.3933</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4158</v>
+        <v>-0.3135</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.16</v>
+        <v>-0.0798</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2754</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>18.7979</v>
+        <v>18.798</v>
       </c>
       <c r="E11" t="n">
-        <v>16.4237</v>
+        <v>16.4235</v>
       </c>
       <c r="F11" t="n">
-        <v>2.374399999999999</v>
+        <v>2.3744</v>
       </c>
       <c r="G11" t="n">
         <v>3.2969</v>
@@ -1312,13 +1312,13 @@
         <v>18.6054</v>
       </c>
       <c r="S11" t="n">
-        <v>1.782</v>
+        <v>1.7821</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7234</v>
+        <v>-0.7233999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5057</v>
+        <v>2.5055</v>
       </c>
       <c r="V11" t="n">
         <v>6.864</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.3336</v>
+        <v>5.7475</v>
       </c>
       <c r="E12" t="n">
-        <v>7.0048</v>
+        <v>7.3118</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6713</v>
+        <v>-1.5643</v>
       </c>
       <c r="G12" t="n">
         <v>5.2276</v>
@@ -1390,13 +1390,13 @@
         <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9321</v>
+        <v>-0.5181</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9151</v>
+        <v>-0.6081</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0169</v>
+        <v>0.09</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3329</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9709</v>
+        <v>1.2057</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1981</v>
+        <v>1.3794</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2272</v>
+        <v>-0.1737</v>
       </c>
       <c r="G13" t="n">
         <v>0.844</v>
@@ -1468,13 +1468,13 @@
         <v>1.5668</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2813</v>
+        <v>0.5161</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1492</v>
+        <v>0.3305</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1321</v>
+        <v>0.1856</v>
       </c>
       <c r="V13" t="n">
         <v>1.2166</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>J. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.229</v>
+        <v>-0.9065</v>
       </c>
       <c r="E14" t="n">
-        <v>0.127</v>
+        <v>1.1162</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3559</v>
+        <v>-2.0226</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2224</v>
+        <v>0.1839</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8435</v>
+        <v>1.674</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6211</v>
+        <v>-1.4902</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7464</v>
+        <v>1.6557</v>
       </c>
       <c r="K14" t="n">
-        <v>0.706</v>
+        <v>2.2167</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0404</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.524</v>
+        <v>-1.4718</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1375</v>
+        <v>-0.5427</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6615</v>
+        <v>-0.9292</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1569</v>
+        <v>-0.5627</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0257</v>
+        <v>-0.3288</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1312</v>
+        <v>-0.2339</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2166</v>
+        <v>-0.7235</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6659</v>
+        <v>0.7685</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5507</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. PORTILLA QUEIRO</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.387</v>
+        <v>-1.0255</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7441</v>
+        <v>-0.5894</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6429</v>
+        <v>-0.4361</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.943</v>
+        <v>0.2224</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1851</v>
+        <v>0.8435</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7579</v>
+        <v>-0.6211</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9475</v>
+        <v>0.7464</v>
       </c>
       <c r="K15" t="n">
-        <v>0.17</v>
+        <v>0.706</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7775</v>
+        <v>0.0404</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.8905</v>
+        <v>-0.524</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3551</v>
+        <v>0.1375</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.5354</v>
+        <v>-0.6615</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.9585</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.917</v>
+        <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9585</v>
+        <v>0.5875</v>
       </c>
       <c r="S15" t="n">
-        <v>1.632</v>
+        <v>0.3604</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.3094</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8986</v>
+        <v>0.051</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8825</v>
+        <v>-1.2166</v>
       </c>
       <c r="W15" t="n">
-        <v>1.492</v>
+        <v>-0.6659</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3905</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GONZALEZ VAZQUEZ</t>
+          <t>N. LAGARES COUCE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.4006</v>
+        <v>-1.3103</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8092</v>
+        <v>0.3477</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2098</v>
+        <v>-1.6579</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1839</v>
+        <v>-0.915</v>
       </c>
       <c r="H16" t="n">
-        <v>1.674</v>
+        <v>0.8176</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4902</v>
+        <v>-1.7327</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6557</v>
+        <v>1.7026</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2167</v>
+        <v>1.6978</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5610000000000001</v>
+        <v>0.0048</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4718</v>
+        <v>-2.6176</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5427</v>
+        <v>-0.8801</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9292</v>
+        <v>-1.7375</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0568</v>
+        <v>-0.6706</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6358</v>
+        <v>-0.6511</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.421</v>
+        <v>-0.0196</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7235</v>
+        <v>0.2754</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7685</v>
+        <v>0.2754</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. LAGARES COUCE</t>
+          <t>L. PORTILLA QUEIRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5417</v>
+        <v>-2.6823</v>
       </c>
       <c r="E17" t="n">
-        <v>0.143</v>
+        <v>-1.6651</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6847</v>
+        <v>-1.0172</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.915</v>
+        <v>-2.943</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8176</v>
+        <v>-1.1851</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7327</v>
+        <v>-1.7579</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7026</v>
+        <v>0.9475</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6978</v>
+        <v>0.17</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0048</v>
+        <v>0.7775</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6176</v>
+        <v>-3.8905</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8801</v>
+        <v>-1.3551</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7375</v>
+        <v>-2.5354</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9792</v>
+        <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.902</v>
+        <v>0.3367</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8557</v>
+        <v>-0.1876</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0463</v>
+        <v>0.5243</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2754</v>
+        <v>1.8825</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2754</v>
+        <v>1.492</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.7695</v>
+        <v>-3.7428</v>
       </c>
       <c r="E18" t="n">
         <v>-1.9292</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8403</v>
+        <v>-1.8136</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6143</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2727</v>
+        <v>-0.246</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0418</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.231</v>
+        <v>-0.2042</v>
       </c>
       <c r="V18" t="n">
         <v>-1.8825</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.5268</v>
+        <v>-4.935</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6267</v>
+        <v>-2.115</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.9001</v>
+        <v>-2.8199</v>
       </c>
       <c r="G19" t="n">
         <v>-2.4584</v>
@@ -1936,13 +1936,13 @@
         <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6352</v>
+        <v>-0.0434</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7369</v>
+        <v>-0.2253</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1017</v>
+        <v>0.1819</v>
       </c>
       <c r="V19" t="n">
         <v>-2.4332</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.718</v>
+        <v>-5.1575</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5352</v>
+        <v>-1.9212</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1829</v>
+        <v>-3.2363</v>
       </c>
       <c r="G20" t="n">
         <v>0.0941</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.2344</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0163</v>
+        <v>-0.4023</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2214</v>
+        <v>0.1679</v>
       </c>
       <c r="V20" t="n">
         <v>-1.492</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.5297</v>
+        <v>-5.9913</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8212</v>
+        <v>-4.3095</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7085</v>
+        <v>-1.6818</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9384</v>
@@ -2092,13 +2092,13 @@
         <v>1.7626</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2584</v>
+        <v>-0.72</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2122</v>
+        <v>-0.7005</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0463</v>
+        <v>-0.0196</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1578</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-18.7978</v>
+        <v>-18.798</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.374300000000001</v>
+        <v>-2.3743</v>
       </c>
       <c r="F22" t="n">
-        <v>-16.4236</v>
+        <v>-16.4234</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2971</v>
+        <v>-3.297099999999999</v>
       </c>
       <c r="H22" t="n">
         <v>5.4423</v>
@@ -2170,22 +2170,22 @@
         <v>11.7507</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7819</v>
+        <v>-1.782</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.5055</v>
+        <v>-2.5056</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7235</v>
+        <v>0.7233999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-6.864</v>
+        <v>-6.863999999999999</v>
       </c>
       <c r="W22" t="n">
         <v>2.6385</v>
       </c>
       <c r="X22" t="n">
-        <v>-9.502599999999999</v>
+        <v>-9.502600000000001</v>
       </c>
     </row>
   </sheetData>
